--- a/data/trans_dic/P12_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P12_1_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces</t>
+          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,52; 18,12</t>
+          <t>12,75; 18,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,11; 15,1</t>
+          <t>10,25; 15,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,74; 17,07</t>
+          <t>11,45; 16,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,41; 17,82</t>
+          <t>12,48; 18,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,89; 21,5</t>
+          <t>15,93; 21,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,76; 29,38</t>
+          <t>22,44; 29,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,9; 21,08</t>
+          <t>15,07; 21,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,96; 21,5</t>
+          <t>16,91; 21,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,04; 19,0</t>
+          <t>15,05; 18,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,23; 21,52</t>
+          <t>17,17; 21,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,94; 18,02</t>
+          <t>14,19; 18,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,39; 19,08</t>
+          <t>15,39; 19,06</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,42; 20,46</t>
+          <t>15,51; 20,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,8; 18,73</t>
+          <t>13,88; 18,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 12,49</t>
+          <t>8,7; 12,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,01</t>
+          <t>3,91; 10,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,0; 26,79</t>
+          <t>21,11; 26,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,86; 26,07</t>
+          <t>20,8; 26,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,21; 17,92</t>
+          <t>13,13; 17,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 19,89</t>
+          <t>15,73; 19,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,9; 22,66</t>
+          <t>18,95; 22,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 21,86</t>
+          <t>18,11; 21,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 14,47</t>
+          <t>11,43; 14,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 14,59</t>
+          <t>8,08; 14,65</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 20,26</t>
+          <t>14,33; 20,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,49; 17,69</t>
+          <t>12,34; 17,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 12,92</t>
+          <t>8,41; 12,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 17,51</t>
+          <t>12,05; 18,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,77; 26,0</t>
+          <t>20,2; 26,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,39; 29,17</t>
+          <t>22,5; 29,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,8; 19,65</t>
+          <t>14,0; 19,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 63,73</t>
+          <t>16,54; 66,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,01; 22,51</t>
+          <t>18,19; 22,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,97; 22,34</t>
+          <t>18,21; 22,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,99; 15,51</t>
+          <t>11,89; 15,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,63; 49,96</t>
+          <t>15,52; 50,48</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,8; 19,5</t>
+          <t>14,7; 19,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,8; 21,09</t>
+          <t>15,95; 20,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 14,59</t>
+          <t>10,27; 14,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 17,35</t>
+          <t>12,39; 17,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,5; 25,64</t>
+          <t>20,47; 25,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,92; 31,65</t>
+          <t>25,82; 31,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 19,78</t>
+          <t>14,86; 19,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,49; 23,24</t>
+          <t>16,53; 23,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,41; 21,99</t>
+          <t>18,6; 22,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,66; 25,73</t>
+          <t>21,89; 25,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 16,45</t>
+          <t>13,28; 16,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,64; 19,74</t>
+          <t>15,68; 19,57</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,21</t>
+          <t>15,67; 18,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,48; 17,05</t>
+          <t>14,58; 17,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,46; 12,77</t>
+          <t>10,56; 12,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,06</t>
+          <t>9,87; 14,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,9; 23,79</t>
+          <t>21,05; 23,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,45; 27,51</t>
+          <t>24,55; 27,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,38; 18,03</t>
+          <t>15,43; 18,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,59; 38,01</t>
+          <t>18,47; 38,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,66; 20,82</t>
+          <t>18,77; 20,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,97; 22,05</t>
+          <t>20,01; 22,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,37; 15,12</t>
+          <t>13,41; 15,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,19; 26,29</t>
+          <t>15,23; 26,56</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces</t>
+          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86874; 125737</t>
+          <t>88469; 125955</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70949; 105900</t>
+          <t>71871; 106598</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79090; 114981</t>
+          <t>77111; 113638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78761; 113114</t>
+          <t>79181; 114230</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>109388; 147973</t>
+          <t>109686; 149162</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>158420; 204494</t>
+          <t>156202; 203975</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99867; 141265</t>
+          <t>101028; 141313</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>114629; 145294</t>
+          <t>114287; 143549</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>207898; 262679</t>
+          <t>208057; 260855</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>240793; 300691</t>
+          <t>239952; 297872</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>187324; 242126</t>
+          <t>190689; 242470</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>201665; 250026</t>
+          <t>201607; 249783</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>148329; 196756</t>
+          <t>149156; 198863</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>140362; 190444</t>
+          <t>141169; 191158</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87325; 127664</t>
+          <t>88927; 128165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54649; 131371</t>
+          <t>46590; 129253</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>203353; 259444</t>
+          <t>204414; 260842</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>214893; 268539</t>
+          <t>214208; 270325</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>137816; 186926</t>
+          <t>136920; 184272</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>151697; 190480</t>
+          <t>150674; 188562</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>364792; 437429</t>
+          <t>365702; 440386</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>371118; 447528</t>
+          <t>370716; 446013</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>233382; 298845</t>
+          <t>236148; 300555</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>185828; 313820</t>
+          <t>173765; 315036</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98466; 137485</t>
+          <t>97203; 139492</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94613; 134058</t>
+          <t>93498; 132962</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62497; 98119</t>
+          <t>63862; 97861</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81612; 123421</t>
+          <t>84941; 131226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>135195; 177766</t>
+          <t>138162; 179731</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>172892; 225283</t>
+          <t>173752; 224464</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>108029; 153749</t>
+          <t>109578; 151652</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>157048; 594807</t>
+          <t>154373; 621360</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>245394; 306710</t>
+          <t>247827; 306874</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>274889; 341779</t>
+          <t>278640; 347932</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184837; 239214</t>
+          <t>183394; 239448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>256076; 818359</t>
+          <t>254267; 826829</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>139424; 183728</t>
+          <t>138526; 183257</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149760; 199907</t>
+          <t>151120; 198693</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93737; 136626</t>
+          <t>96226; 135480</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>116139; 160773</t>
+          <t>114800; 157726</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>212964; 266277</t>
+          <t>212589; 267576</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>272645; 332967</t>
+          <t>271599; 333100</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>153895; 206238</t>
+          <t>154900; 206489</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>180412; 254321</t>
+          <t>180923; 253649</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>364686; 435649</t>
+          <t>368443; 443289</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>433098; 514495</t>
+          <t>437655; 512547</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>262095; 325560</t>
+          <t>262859; 327654</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>316063; 398980</t>
+          <t>316988; 395574</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>511610; 596679</t>
+          <t>513326; 598104</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>495880; 583831</t>
+          <t>499111; 596268</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>354814; 433259</t>
+          <t>358217; 431445</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>335345; 486187</t>
+          <t>341352; 487179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>706186; 803807</t>
+          <t>711226; 805335</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>867953; 976539</t>
+          <t>871659; 977191</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>544270; 637888</t>
+          <t>545872; 637115</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>680531; 1391476</t>
+          <t>676326; 1420058</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1242138; 1385570</t>
+          <t>1249092; 1376110</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1392870; 1538054</t>
+          <t>1395615; 1537357</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>926931; 1047567</t>
+          <t>929739; 1047161</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1081742; 1871800</t>
+          <t>1084551; 1891444</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P12_1_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,75; 18,15</t>
+          <t>12,69; 17,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 15,2</t>
+          <t>10,23; 15,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,45; 16,87</t>
+          <t>11,48; 16,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,48; 18,0</t>
+          <t>12,48; 17,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,93; 21,67</t>
+          <t>15,94; 21,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,44; 29,3</t>
+          <t>22,69; 29,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,07; 21,08</t>
+          <t>14,87; 20,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,91; 21,24</t>
+          <t>16,58; 20,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,05; 18,87</t>
+          <t>15,0; 19,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,17; 21,31</t>
+          <t>17,23; 21,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,19; 18,04</t>
+          <t>13,86; 17,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,39; 19,06</t>
+          <t>15,14; 18,47</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,51; 20,68</t>
+          <t>15,08; 20,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,88; 18,8</t>
+          <t>13,94; 18,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,54</t>
+          <t>8,55; 12,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,84</t>
+          <t>8,67; 12,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,11; 26,94</t>
+          <t>21,04; 26,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,8; 26,24</t>
+          <t>20,85; 26,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,13; 17,67</t>
+          <t>13,14; 17,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 19,69</t>
+          <t>15,89; 20,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,95; 22,82</t>
+          <t>19,18; 22,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,11; 21,79</t>
+          <t>17,9; 21,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 14,55</t>
+          <t>11,43; 14,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 14,65</t>
+          <t>13,0; 15,74</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,33; 20,56</t>
+          <t>14,12; 20,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 17,55</t>
+          <t>12,55; 18,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,88</t>
+          <t>8,43; 12,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,05; 18,62</t>
+          <t>11,71; 17,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,2; 26,28</t>
+          <t>20,08; 26,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,5; 29,07</t>
+          <t>22,28; 28,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,0; 19,38</t>
+          <t>14,02; 19,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,54; 66,57</t>
+          <t>16,21; 21,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 22,53</t>
+          <t>18,09; 22,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,21; 22,74</t>
+          <t>18,32; 22,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 15,53</t>
+          <t>11,8; 15,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,52; 50,48</t>
+          <t>14,59; 18,53</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,7; 19,45</t>
+          <t>14,64; 19,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,95; 20,96</t>
+          <t>15,74; 20,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 14,47</t>
+          <t>10,2; 14,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 17,02</t>
+          <t>12,43; 17,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,47; 25,76</t>
+          <t>20,53; 25,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,82; 31,67</t>
+          <t>25,84; 31,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 19,8</t>
+          <t>14,94; 19,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,53; 23,18</t>
+          <t>20,01; 24,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,6; 22,38</t>
+          <t>18,09; 21,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,89; 25,63</t>
+          <t>21,58; 25,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 16,55</t>
+          <t>13,01; 16,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,68; 19,57</t>
+          <t>16,9; 20,29</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,67; 18,25</t>
+          <t>15,64; 18,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 17,42</t>
+          <t>14,47; 17,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,56; 12,72</t>
+          <t>10,62; 12,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,87; 14,08</t>
+          <t>12,18; 14,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 23,83</t>
+          <t>21,04; 23,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,55; 27,52</t>
+          <t>24,43; 27,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,43; 18,01</t>
+          <t>15,32; 18,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 38,79</t>
+          <t>18,39; 20,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,77; 20,68</t>
+          <t>18,66; 20,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,01; 22,04</t>
+          <t>19,94; 21,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,41; 15,11</t>
+          <t>13,36; 15,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,23; 26,56</t>
+          <t>15,67; 17,33</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96147</t>
+          <t>102982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>128669</t>
+          <t>136303</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>224815</t>
+          <t>239285</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88469; 125955</t>
+          <t>88062; 123752</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>71871; 106598</t>
+          <t>71736; 106898</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77111; 113638</t>
+          <t>77304; 113090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79181; 114230</t>
+          <t>86105; 123565</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>109686; 149162</t>
+          <t>109735; 149496</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>156202; 203975</t>
+          <t>157975; 205691</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>101028; 141313</t>
+          <t>99660; 140158</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>114287; 143549</t>
+          <t>121546; 152147</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>208057; 260855</t>
+          <t>207362; 263287</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>239952; 297872</t>
+          <t>240791; 300105</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190689; 242470</t>
+          <t>186299; 241317</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>201607; 249783</t>
+          <t>215428; 262864</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98472</t>
+          <t>110231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>170253</t>
+          <t>192343</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>268724</t>
+          <t>302574</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>149156; 198863</t>
+          <t>145041; 196521</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>141169; 191158</t>
+          <t>141756; 191536</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88927; 128165</t>
+          <t>87387; 131231</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46590; 129253</t>
+          <t>90940; 132930</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>204414; 260842</t>
+          <t>203716; 258607</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>214208; 270325</t>
+          <t>214797; 274188</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>136920; 184272</t>
+          <t>137048; 183402</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>150674; 188562</t>
+          <t>170044; 214861</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>365702; 440386</t>
+          <t>370135; 441977</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>370716; 446013</t>
+          <t>366357; 445625</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>236148; 300555</t>
+          <t>235989; 299435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>173765; 315036</t>
+          <t>275461; 333676</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103582</t>
+          <t>112758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>333775</t>
+          <t>152261</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>437357</t>
+          <t>265019</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97203; 139492</t>
+          <t>95778; 138196</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93498; 132962</t>
+          <t>95089; 136710</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63862; 97861</t>
+          <t>64058; 97018</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84941; 131226</t>
+          <t>94058; 139275</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>138162; 179731</t>
+          <t>137303; 179809</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>173752; 224464</t>
+          <t>172069; 223150</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>109578; 151652</t>
+          <t>109734; 151617</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>154373; 621360</t>
+          <t>131631; 174265</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>247827; 306874</t>
+          <t>246459; 304634</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>278640; 347932</t>
+          <t>280212; 344345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183394; 239448</t>
+          <t>181927; 237830</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>254267; 826829</t>
+          <t>235598; 299399</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136794</t>
+          <t>146122</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>225806</t>
+          <t>246686</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>362601</t>
+          <t>392808</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>138526; 183257</t>
+          <t>137896; 182661</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>151120; 198693</t>
+          <t>149179; 198103</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96226; 135480</t>
+          <t>95487; 135520</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>114800; 157726</t>
+          <t>123062; 172808</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>212589; 267576</t>
+          <t>213239; 267614</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>271599; 333100</t>
+          <t>271817; 329475</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>154900; 206489</t>
+          <t>155785; 206696</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>180923; 253649</t>
+          <t>223804; 272936</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>368443; 443289</t>
+          <t>358281; 434189</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>437655; 512547</t>
+          <t>431530; 510484</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>262859; 327654</t>
+          <t>257413; 322692</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>316988; 395574</t>
+          <t>356282; 427761</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>434995</t>
+          <t>472094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>858503</t>
+          <t>727593</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1293498</t>
+          <t>1199687</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>513326; 598104</t>
+          <t>512557; 598780</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>499111; 596268</t>
+          <t>495542; 587182</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>358217; 431445</t>
+          <t>360374; 434948</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>341352; 487179</t>
+          <t>430206; 515362</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>711226; 805335</t>
+          <t>710915; 807951</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>871659; 977191</t>
+          <t>867361; 978350</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>545872; 637115</t>
+          <t>542145; 637600</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>676326; 1420058</t>
+          <t>686740; 769919</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1249092; 1376110</t>
+          <t>1241836; 1377343</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1395615; 1537357</t>
+          <t>1390928; 1532087</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>929739; 1047161</t>
+          <t>926230; 1045018</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1084551; 1891444</t>
+          <t>1138565; 1259407</t>
         </is>
       </c>
     </row>
